--- a/stories/arbres/TREE-SEC-002.xlsx
+++ b/stories/arbres/TREE-SEC-002.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Hugo est à la ferme avec Maman. Ils vont au village. Au chemin, il y a un feu. Hugo s'arrête. Ses pieds restent sur le trottoir en attendant. Il attend le feu vert. Sa main est dans la main de Maman. Maman est l'adulte. On avance avec Maman. Papa range le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe par la cuisine de la ferme. Ça sent le lait. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le panier. Une vache meugle loin. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2549,6 +2601,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2717,6 +2774,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Le vent est doux. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. Un oiseau chante. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. Le seau cliquette. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau bleu. L'herbe sent bon. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3889,6 +3981,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4154,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Un oiseau chante. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4219,6 +4321,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4385,6 +4492,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. Le seau cliquette. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4547,6 +4659,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4713,6 +4830,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. La terre est sèche. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4875,6 +4997,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5041,6 +5168,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Le vent est doux. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5229,6 +5361,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5397,6 +5534,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5559,6 +5701,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5725,6 +5872,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5887,6 +6039,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6053,6 +6210,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6215,6 +6377,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6381,6 +6548,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe par le jardin. L'herbe est froide. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6565,6 +6737,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -6737,6 +6914,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6923,6 +7105,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7089,6 +7276,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le panier. Un oiseau chante. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,6 +7469,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7445,6 +7642,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Un oiseau chante. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,6 +7809,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7773,6 +7980,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. Le seau cliquette. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7935,6 +8147,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8101,6 +8318,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. La terre est sèche. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8263,6 +8485,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8429,6 +8656,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau bleu. Le seau cliquette. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8617,6 +8849,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8785,6 +9022,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8947,6 +9189,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9113,6 +9360,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9275,6 +9527,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9441,6 +9698,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9603,6 +9865,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9769,6 +10036,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. La terre est sèche. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9957,6 +10229,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10125,6 +10402,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. La terre est sèche. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10287,6 +10569,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10453,6 +10740,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. Une vache meugle loin. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10615,6 +10907,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10781,6 +11078,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. L'herbe sent bon. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10943,6 +11245,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11109,6 +11416,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo passe par la chambre. La couverture est douce. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11293,6 +11605,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
     </row>
@@ -11465,6 +11782,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11651,6 +11973,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11817,6 +12144,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le panier. Une vache meugle loin. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12005,6 +12337,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12173,6 +12510,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12335,6 +12677,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12501,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12663,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12829,6 +13186,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12991,6 +13353,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13157,6 +13524,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le seau bleu. L'herbe sent bon. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13345,6 +13717,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13513,6 +13890,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. La terre est sèche. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13675,6 +14057,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13841,6 +14228,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. Une vache meugle loin. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14003,6 +14395,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14169,6 +14566,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. L'herbe sent bon. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14331,6 +14733,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14497,6 +14904,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a choisi le doudou. Le vent est doux. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14685,6 +15097,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14853,6 +15270,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Tom. Une vache meugle loin. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15015,6 +15437,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15181,6 +15608,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Léa. L'herbe sent bon. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15343,6 +15775,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15509,6 +15946,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo salue Sami. Le vent est doux. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15671,6 +16113,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15689,7 +16136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +16209,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-002.xlsx
+++ b/stories/arbres/TREE-SEC-002.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Hugo est à la ferme avec Maman. Ils vont au village. Au chemin, il y a un feu. Hugo s'arrête. Ses pieds restent sur le trottoir en attendant. Il attend le feu vert. Sa main est dans la main de Maman. Maman est l'adulte. On avance avec Maman. Papa range le foin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Hugo passe par la cuisine de la ferme. Ça sent le lait. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1884,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2060,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2252,7 @@
           <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2424,7 @@
           <t>narrateur|Hugo a choisi le panier. Une vache meugle loin. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2620,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2792,7 @@
           <t>narrateur|Hugo salue Tom. Le vent est doux. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2960,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3132,7 @@
           <t>narrateur|Hugo salue Léa. Un oiseau chante. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3472,7 @@
           <t>narrateur|Hugo salue Sami. Le seau cliquette. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3812,7 @@
           <t>narrateur|Hugo a choisi le seau bleu. L'herbe sent bon. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3988,6 +4008,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4159,6 +4180,7 @@
           <t>narrateur|Hugo salue Tom. Un oiseau chante. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4326,6 +4348,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4497,6 +4520,7 @@
           <t>narrateur|Hugo salue Léa. Le seau cliquette. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4664,6 +4688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4835,6 +4860,7 @@
           <t>narrateur|Hugo salue Sami. La terre est sèche. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5002,6 +5028,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5173,6 +5200,7 @@
           <t>narrateur|Hugo a choisi le doudou. Le vent est doux. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5368,6 +5396,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5539,6 +5568,7 @@
           <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5706,6 +5736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5877,6 +5908,7 @@
           <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6044,6 +6076,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6215,6 +6248,7 @@
           <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6382,6 +6416,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6553,6 +6588,7 @@
           <t>narrateur|Hugo passe par le jardin. L'herbe est froide. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6744,6 +6780,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6919,6 +6956,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7110,6 +7148,7 @@
           <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7281,6 +7320,7 @@
           <t>narrateur|Hugo a choisi le panier. Un oiseau chante. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7476,6 +7516,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7647,6 +7688,7 @@
           <t>narrateur|Hugo salue Tom. Un oiseau chante. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7814,6 +7856,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7985,6 +8028,7 @@
           <t>narrateur|Hugo salue Léa. Le seau cliquette. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8152,6 +8196,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8323,6 +8368,7 @@
           <t>narrateur|Hugo salue Sami. La terre est sèche. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8490,6 +8536,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8661,6 +8708,7 @@
           <t>narrateur|Hugo a choisi le seau bleu. Le seau cliquette. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8856,6 +8904,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9027,6 +9076,7 @@
           <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9194,6 +9244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9365,6 +9416,7 @@
           <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9532,6 +9584,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9703,6 +9756,7 @@
           <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9870,6 +9924,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10041,6 +10096,7 @@
           <t>narrateur|Hugo a choisi le doudou. La terre est sèche. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10236,6 +10292,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10407,6 +10464,7 @@
           <t>narrateur|Hugo salue Tom. La terre est sèche. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10574,6 +10632,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10745,6 +10804,7 @@
           <t>narrateur|Hugo salue Léa. Une vache meugle loin. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10912,6 +10972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11083,6 +11144,7 @@
           <t>narrateur|Hugo salue Sami. L'herbe sent bon. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11250,6 +11312,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11421,6 +11484,7 @@
           <t>narrateur|Hugo passe par la chambre. La couverture est douce. Puis ils vont au chemin. Hugo attend le feu vert. Pieds sur le trottoir en attendant. Main dans la main de Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11612,6 +11676,7 @@
           <t>narrateur|On attend quoi ? Le feu vert. Avec qui ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11787,6 +11852,7 @@
           <t>narrateur|Oui. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo retient : feu vert, main, adulte, trottoir en attendant. La main est dans la main de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11978,6 +12044,7 @@
           <t>narrateur|On peut prendre le panier, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12149,6 +12216,7 @@
           <t>narrateur|Hugo a choisi le panier. Une vache meugle loin. Hugo tient le panier contre son manteau. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12344,6 +12412,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12515,6 +12584,7 @@
           <t>narrateur|Hugo salue Tom. Le seau cliquette. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12682,6 +12752,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12853,6 +12924,7 @@
           <t>narrateur|Hugo salue Léa. La terre est sèche. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13020,6 +13092,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13191,6 +13264,7 @@
           <t>narrateur|Hugo salue Sami. Une vache meugle loin. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13358,6 +13432,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13529,6 +13604,7 @@
           <t>narrateur|Hugo a choisi le seau bleu. L'herbe sent bon. Hugo tient le seau bleu. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman, l'adulte. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13724,6 +13800,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13895,6 +13972,7 @@
           <t>narrateur|Hugo salue Tom. La terre est sèche. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14062,6 +14140,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14233,6 +14312,7 @@
           <t>narrateur|Hugo salue Léa. Une vache meugle loin. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14400,6 +14480,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14571,6 +14652,7 @@
           <t>narrateur|Hugo salue Sami. L'herbe sent bon. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14738,6 +14820,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14909,6 +14992,7 @@
           <t>narrateur|Hugo a choisi le doudou. Le vent est doux. Hugo tient le doudou. Il attend le feu vert. Pieds sur le trottoir en attendant. Main de Maman. La main est dans la main de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15104,6 +15188,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15275,6 +15360,7 @@
           <t>narrateur|Hugo salue Tom. Une vache meugle loin. Tom attend de l'autre côté, près d'un adulte. Hugo reste avec Maman. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15442,6 +15528,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15613,6 +15700,7 @@
           <t>narrateur|Hugo salue Léa. L'herbe sent bon. Léa salue de la main. Hugo reste avec Maman, l'adulte. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15780,6 +15868,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15951,6 +16040,7 @@
           <t>narrateur|Hugo salue Sami. Le vent est doux. Sami a un cartable. Hugo avance avec Maman, au feu vert. Les pieds restent sur le trottoir en attendant. On attend le feu vert. La main tient la main de l'adulte. On avance avec l'adulte. Hugo dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16118,6 +16208,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16136,7 +16227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16216,6 +16307,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16417,6 +16522,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
